--- a/POTAL_D15_Intelligence_Market.xlsx
+++ b/POTAL_D15_Intelligence_Market.xlsx
@@ -1,17 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="경쟁사변동이력" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="경쟁사별현황" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="시장동향" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cron스캔결과" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D15 Dashboard" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="CW21_20260328" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="경쟁사변동이력" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="경쟁사별현황" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="시장동향" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Cron스캔결과" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="D15 Dashboard" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -21,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="18">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -136,6 +137,9 @@
     <font>
       <name val="Arial"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -184,7 +188,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -242,6 +246,7 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -491,6 +496,114 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" style="10" min="1" max="1"/>
+    <col width="25" customWidth="1" style="10" min="2" max="2"/>
+    <col width="60" customWidth="1" style="10" min="3" max="3"/>
+    <col width="40" customWidth="1" style="10" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="21" t="inlineStr">
+        <is>
+          <t>시간</t>
+        </is>
+      </c>
+      <c r="B1" s="21" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="C1" s="21" t="inlineStr">
+        <is>
+          <t>내용</t>
+        </is>
+      </c>
+      <c r="D1" s="21" t="inlineStr">
+        <is>
+          <t>영향</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-03-28 23:30 KST</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>v3 파이프라인 완성</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>경쟁사 대비 기술 우위 확보</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Avalara/Zonos는 AI 기반 → 비용 발생, POTAL은 rule-based → $0</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-03-28 23:30 KST</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>21 Section 전체 커버</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Avalara(20+ sections), Zonos(제한적) 대비 WCO 완전 커버</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>벤치마크 비교 자료 사용 가능</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-03-28 23:30 KST</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>595 codified rules</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>WCO Section/Chapter Notes 95%+ 코드화</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>규칙 기반 분류 신뢰도 업계 최고 수준</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
@@ -595,7 +708,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1090,7 +1203,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1183,7 +1296,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1264,7 +1377,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/POTAL_D15_Intelligence_Market.xlsx
+++ b/POTAL_D15_Intelligence_Market.xlsx
@@ -7,12 +7,13 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="CW21_20260328" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="경쟁사변동이력" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="경쟁사별현황" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="시장동향" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Cron스캔결과" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="D15 Dashboard" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="CW22B_DataCollection" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="CW21_20260328" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="경쟁사변동이력" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="경쟁사별현황" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="시장동향" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Cron스캔결과" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="D15 Dashboard" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -500,6 +501,96 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" style="10" min="1" max="1"/>
+    <col width="80" customWidth="1" style="10" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="21" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B1" s="21" t="inlineStr">
+        <is>
+          <t>내용</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>날짜</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-03-29 21:00 KST</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>개선 사항</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Google OAuth 사용자도 회사명/국가/업종 필수 수집</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>효과</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Exit 전략 핵심 데이터(셀러 프로필) 수집률 100% 보장</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>이전</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Google OAuth 가입 시 프로필 정보 없이 바로 대시보드</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>이후</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>complete-profile 페이지에서 필수 입력 후 대시보드</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -532,66 +623,66 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>2026-03-28 23:30 KST</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="9" t="inlineStr">
         <is>
           <t>v3 파이프라인 완성</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>경쟁사 대비 기술 우위 확보</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="9" t="inlineStr">
         <is>
           <t>Avalara/Zonos는 AI 기반 → 비용 발생, POTAL은 rule-based → $0</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>2026-03-28 23:30 KST</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="9" t="inlineStr">
         <is>
           <t>21 Section 전체 커버</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="9" t="inlineStr">
         <is>
           <t>Avalara(20+ sections), Zonos(제한적) 대비 WCO 완전 커버</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="9" t="inlineStr">
         <is>
           <t>벤치마크 비교 자료 사용 가능</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>2026-03-28 23:30 KST</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>595 codified rules</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="9" t="inlineStr">
         <is>
           <t>WCO Section/Chapter Notes 95%+ 코드화</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="9" t="inlineStr">
         <is>
           <t>규칙 기반 분류 신뢰도 업계 최고 수준</t>
         </is>
@@ -602,7 +693,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -708,7 +799,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1203,7 +1294,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1296,7 +1387,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1377,7 +1468,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
